--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260818.xlsx
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>大成</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>2,082,678</t>
+          <t>21,744,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>大成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>21,744,000</t>
+          <t>2,082,678</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
